--- a/data/summer_scheduler_template.xlsx
+++ b/data/summer_scheduler_template.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,97 +460,99 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>current_day</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>schedule_start_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Usually 1 for a fresh run</t>
+          <t>First workday of summer cleaning</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>target_end_day</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>20</v>
+          <t>work_on_weekends</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Target workday number</t>
+          <t>True if Saturdays/Sundays count as workdays</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>scheduled_shift_hours_per_day</t>
+          <t>current_day</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paid shift length</t>
+          <t>Usually 1 for a fresh run</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lunch_hours_per_day</t>
+          <t>target_end_day</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lunch time</t>
+          <t>Target workday number</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>break_hours_per_day</t>
+          <t>scheduled_shift_hours_per_day</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Total break time</t>
+          <t>Paid shift length</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>setup_hours_per_day</t>
+          <t>lunch_hours_per_day</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Setup/opening time</t>
+          <t>Lunch time</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cleanup_hours_per_day</t>
+          <t>break_hours_per_day</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -558,59 +560,59 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleanup/lockup time</t>
+          <t>Total break time</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>productive_hours_per_staff_per_day</t>
+          <t>setup_hours_per_day</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.75</v>
+        <v>0.25</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Real productive time per worker</t>
+          <t>Setup/opening time</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>include_deep_clean</t>
-        </is>
-      </c>
-      <c r="B11" t="b">
-        <v>1</v>
+          <t>cleanup_hours_per_day</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Run deep clean tasks</t>
+          <t>Cleanup/lockup time</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>include_strip</t>
-        </is>
-      </c>
-      <c r="B12" t="b">
-        <v>1</v>
+          <t>productive_hours_per_staff_per_day</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6.75</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Run strip tasks</t>
+          <t>Real productive time per worker</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>include_wax</t>
+          <t>include_deep_clean</t>
         </is>
       </c>
       <c r="B13" t="b">
@@ -618,14 +620,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Run wax tasks</t>
+          <t>Run deep clean tasks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>include_carpet</t>
+          <t>include_strip</t>
         </is>
       </c>
       <c r="B14" t="b">
@@ -633,244 +635,274 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Run carpet tasks</t>
+          <t>Run strip tasks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>include_exterior</t>
+          <t>include_wax</t>
         </is>
       </c>
       <c r="B15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Run exterior tasks</t>
+          <t>Run wax tasks</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deep_clean_rate_sqft_per_hour</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>400</v>
+          <t>include_carpet</t>
+        </is>
+      </c>
+      <c r="B16" t="b">
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deep clean production rate</t>
+          <t>Run carpet tasks</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>strip_rate_sqft_per_hour</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>300</v>
+          <t>include_exterior</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Strip production rate</t>
+          <t>Run exterior tasks</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wax_rate_sqft_per_hour</t>
+          <t>deep_clean_rate_sqft_per_hour</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wax production rate</t>
+          <t>Deep clean production rate</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>carpet_rate_sqft_per_hour</t>
+          <t>strip_rate_sqft_per_hour</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carpet production rate</t>
+          <t>Strip production rate</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>exterior_rate_sqft_per_hour</t>
+          <t>wax_rate_sqft_per_hour</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Exterior production rate</t>
+          <t>Wax production rate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wax_coats</t>
+          <t>carpet_rate_sqft_per_hour</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Number of wax coats</t>
+          <t>Carpet production rate</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>transition_hours_per_school</t>
+          <t>exterior_rate_sqft_per_hour</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inter-school logistics time</t>
+          <t>Exterior production rate</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>day_start_time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>7:30 AM</t>
-        </is>
+          <t>wax_coats</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arrival/open</t>
+          <t>Number of wax coats</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_start_time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>7:45 AM</t>
-        </is>
+          <t>transition_hours_per_school</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Work starts</t>
+          <t>Inter-school logistics time</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>first_break_time</t>
+          <t>day_start_time</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>7:30 AM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>First break</t>
+          <t>Arrival/open</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lunch_time</t>
+          <t>work_start_time</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>7:45 AM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Work starts</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>second_break_time</t>
+          <t>first_break_time</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Second break</t>
+          <t>First break</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cleanup_start_time</t>
+          <t>lunch_time</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleanup starts</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>second_break_time</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Second break</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cleanup_start_time</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cleanup starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>day_end_time</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>End of day</t>
         </is>
@@ -1031,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,6 +1430,346 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
         <v>0</v>
       </c>
     </row>
